--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{14BF3FBC-23FE-4A07-9BC2-7BF110E827F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{850E1EF2-2450-44EB-812B-FA2E7DCF241C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -778,7 +778,7 @@
       <c r="J9" s="5"/>
       <c r="L9" s="5">
         <f>SUM(I9:I15)</f>
-        <v>3885.8</v>
+        <v>3849.8</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.3">
@@ -807,7 +807,7 @@
       <c r="J10" s="5"/>
       <c r="L10" s="5">
         <f>L9+I6</f>
-        <v>4634.6200000000008</v>
+        <v>4598.6200000000008</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.3">
@@ -836,7 +836,7 @@
       <c r="J11" s="5"/>
       <c r="L11" s="5">
         <f>L10+I7+I8</f>
-        <v>3637.5050000000001</v>
+        <v>3601.5050000000001</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.3">
@@ -925,7 +925,8 @@
         <v>2128.08</v>
       </c>
       <c r="E15" s="6">
-        <v>1511.27</v>
+        <f>1511.27+36</f>
+        <v>1547.27</v>
       </c>
       <c r="F15">
         <v>2813</v>
@@ -935,7 +936,7 @@
       </c>
       <c r="I15" s="5">
         <f t="shared" si="0"/>
-        <v>616.80999999999995</v>
+        <v>580.80999999999995</v>
       </c>
       <c r="J15" s="5"/>
       <c r="O15" s="7" t="s">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\github_corrigido_dashboard_obrasRev1\github\docs\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2299176A-C19C-40BD-A1D5-6456718FD83A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C358BF-8DF4-4D62-BADE-D5393D7E8BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EAP_PRODUCAO" sheetId="2" r:id="rId1"/>
@@ -953,7 +953,7 @@
         <v>2426.84</v>
       </c>
       <c r="E16" s="2">
-        <v>1747.73</v>
+        <v>1538.59</v>
       </c>
       <c r="F16">
         <v>2735</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
-        <v>679.11000000000013</v>
+        <v>888.25000000000023</v>
       </c>
       <c r="J16" s="5"/>
     </row>
@@ -1109,19 +1109,19 @@
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P27">
         <f>SUM(E3:E16)</f>
-        <v>15619.635000000002</v>
+        <v>15410.495000000003</v>
       </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P28">
         <f>14468.56-P27</f>
-        <v>-1151.0750000000025</v>
+        <v>-941.93500000000313</v>
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P29">
         <f>P28+2135.09</f>
-        <v>984.0149999999976</v>
+        <v>1193.154999999997</v>
       </c>
     </row>
     <row r="34" spans="8:8" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{72C358BF-8DF4-4D62-BADE-D5393D7E8BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA540C8-E5A2-40B7-9983-66D5BB8B77CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -953,7 +953,7 @@
         <v>2426.84</v>
       </c>
       <c r="E16" s="2">
-        <v>1538.59</v>
+        <v>1460.1</v>
       </c>
       <c r="F16">
         <v>2735</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
-        <v>888.25000000000023</v>
+        <v>966.74000000000024</v>
       </c>
       <c r="J16" s="5"/>
     </row>
@@ -1109,19 +1109,19 @@
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P27">
         <f>SUM(E3:E16)</f>
-        <v>15410.495000000003</v>
+        <v>15332.005000000003</v>
       </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P28">
         <f>14468.56-P27</f>
-        <v>-941.93500000000313</v>
+        <v>-863.44500000000335</v>
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P29">
         <f>P28+2135.09</f>
-        <v>1193.154999999997</v>
+        <v>1271.6449999999968</v>
       </c>
     </row>
     <row r="34" spans="8:8" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8AA540C8-E5A2-40B7-9983-66D5BB8B77CE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084374D7-219F-4865-A67B-DF058096A9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -722,7 +722,7 @@
         <v>584</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I16" si="0">D7-E7</f>
+        <f t="shared" ref="I7:I17" si="0">D7-E7</f>
         <v>-473.39499999999998</v>
       </c>
       <c r="J7" s="5"/>
@@ -977,11 +977,18 @@
       <c r="D17" s="3">
         <v>2545.85</v>
       </c>
+      <c r="E17" s="2">
+        <v>78.19</v>
+      </c>
       <c r="F17">
         <v>2361</v>
       </c>
       <c r="G17">
         <v>0</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>2467.66</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{084374D7-219F-4865-A67B-DF058096A9CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31121218-0874-4EA2-8846-FCB06702568F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EAP_PRODUCAO" sheetId="2" r:id="rId1"/>
@@ -978,7 +978,7 @@
         <v>2545.85</v>
       </c>
       <c r="E17" s="2">
-        <v>78.19</v>
+        <v>200.72</v>
       </c>
       <c r="F17">
         <v>2361</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>2467.66</v>
+        <v>2345.13</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31121218-0874-4EA2-8846-FCB06702568F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD6A140-D5A1-4F1F-B02B-0CAC26B11EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -959,7 +959,7 @@
         <v>2735</v>
       </c>
       <c r="G16">
-        <v>5747</v>
+        <v>5246</v>
       </c>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
@@ -978,7 +978,7 @@
         <v>2545.85</v>
       </c>
       <c r="E17" s="2">
-        <v>200.72</v>
+        <v>378.57</v>
       </c>
       <c r="F17">
         <v>2361</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>2345.13</v>
+        <v>2167.2799999999997</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8DD6A140-D5A1-4F1F-B02B-0CAC26B11EF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224A9EBC-ABC2-4488-9D98-6530CCAF7884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -978,7 +978,7 @@
         <v>2545.85</v>
       </c>
       <c r="E17" s="2">
-        <v>378.57</v>
+        <v>487.87</v>
       </c>
       <c r="F17">
         <v>2361</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>2167.2799999999997</v>
+        <v>2057.98</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{224A9EBC-ABC2-4488-9D98-6530CCAF7884}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C64D580-29E9-40FC-91FE-F87705B4D0F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -978,7 +978,8 @@
         <v>2545.85</v>
       </c>
       <c r="E17" s="2">
-        <v>487.87</v>
+        <f>487.87+84.32+43.66</f>
+        <v>615.85</v>
       </c>
       <c r="F17">
         <v>2361</v>
@@ -988,7 +989,7 @@
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>2057.98</v>
+        <v>1930</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C64D580-29E9-40FC-91FE-F87705B4D0F7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F77330-4780-48E6-88FD-AC6520BEC045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -978,8 +978,8 @@
         <v>2545.85</v>
       </c>
       <c r="E17" s="2">
-        <f>487.87+84.32+43.66</f>
-        <v>615.85</v>
+        <f>487.87+84.32+43.66+62.701</f>
+        <v>678.55100000000004</v>
       </c>
       <c r="F17">
         <v>2361</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>1930</v>
+        <v>1867.299</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4F77330-4780-48E6-88FD-AC6520BEC045}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756AE521-D5AA-4E0D-B1B2-BE7BDE482BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -978,8 +978,8 @@
         <v>2545.85</v>
       </c>
       <c r="E17" s="2">
-        <f>487.87+84.32+43.66+62.701</f>
-        <v>678.55100000000004</v>
+        <f>487.87+84.32+43.66+62.701+80.157</f>
+        <v>758.70800000000008</v>
       </c>
       <c r="F17">
         <v>2361</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>1867.299</v>
+        <v>1787.1419999999998</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{756AE521-D5AA-4E0D-B1B2-BE7BDE482BCB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DADB6B-5891-48B4-9806-831A9DEEB64F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -978,8 +978,8 @@
         <v>2545.85</v>
       </c>
       <c r="E17" s="2">
-        <f>487.87+84.32+43.66+62.701+80.157</f>
-        <v>758.70800000000008</v>
+        <f>487.87+84.32+43.66+62.701+80.157+78.58</f>
+        <v>837.28800000000012</v>
       </c>
       <c r="F17">
         <v>2361</v>
@@ -989,7 +989,7 @@
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>1787.1419999999998</v>
+        <v>1708.5619999999999</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C3DADB6B-5891-48B4-9806-831A9DEEB64F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE10B86-95C7-4CE6-BC57-C080B097E222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -978,8 +978,7 @@
         <v>2545.85</v>
       </c>
       <c r="E17" s="2">
-        <f>487.87+84.32+43.66+62.701+80.157+78.58</f>
-        <v>837.28800000000012</v>
+        <v>1038.288</v>
       </c>
       <c r="F17">
         <v>2361</v>
@@ -989,7 +988,7 @@
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>1708.5619999999999</v>
+        <v>1507.5619999999999</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3CE10B86-95C7-4CE6-BC57-C080B097E222}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0887C667-6230-4375-B7F7-B3278770801E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -978,7 +978,7 @@
         <v>2545.85</v>
       </c>
       <c r="E17" s="2">
-        <v>1038.288</v>
+        <v>1160.9380000000001</v>
       </c>
       <c r="F17">
         <v>2361</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>1507.5619999999999</v>
+        <v>1384.9119999999998</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0887C667-6230-4375-B7F7-B3278770801E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D52570A-277F-4667-89FE-143E85753D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EAP_PRODUCAO" sheetId="2" r:id="rId1"/>
@@ -978,7 +978,7 @@
         <v>2545.85</v>
       </c>
       <c r="E17" s="2">
-        <v>1160.9380000000001</v>
+        <v>1247.9380000000001</v>
       </c>
       <c r="F17">
         <v>2361</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>1384.9119999999998</v>
+        <v>1297.9119999999998</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D52570A-277F-4667-89FE-143E85753D31}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B561E8BC-C6B0-4427-94A5-A784A55045FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EAP_PRODUCAO" sheetId="2" r:id="rId1"/>
@@ -978,7 +978,7 @@
         <v>2545.85</v>
       </c>
       <c r="E17" s="2">
-        <v>1247.9380000000001</v>
+        <v>1393.3510000000001</v>
       </c>
       <c r="F17">
         <v>2361</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>1297.9119999999998</v>
+        <v>1152.4989999999998</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B561E8BC-C6B0-4427-94A5-A784A55045FD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6262598-7C2B-4802-B1A9-DAD7F5E41CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -978,7 +978,7 @@
         <v>2545.85</v>
       </c>
       <c r="E17" s="2">
-        <v>1393.3510000000001</v>
+        <v>1255.723</v>
       </c>
       <c r="F17">
         <v>2361</v>
@@ -988,7 +988,7 @@
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>1152.4989999999998</v>
+        <v>1290.127</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6262598-7C2B-4802-B1A9-DAD7F5E41CC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54CDAE3-6C67-45A5-984D-FD9FC6B3F0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -667,7 +667,7 @@
         <v>905.99</v>
       </c>
       <c r="E5" s="2">
-        <v>364.53</v>
+        <v>397.82</v>
       </c>
       <c r="F5" s="4">
         <v>0</v>
@@ -688,7 +688,7 @@
         <v>1089.1400000000001</v>
       </c>
       <c r="E6">
-        <v>340.32</v>
+        <v>364.53</v>
       </c>
       <c r="F6">
         <v>191</v>
@@ -698,7 +698,7 @@
       </c>
       <c r="I6" s="5">
         <f>D6-E6</f>
-        <v>748.82000000000016</v>
+        <v>724.61000000000013</v>
       </c>
       <c r="J6" s="5"/>
     </row>
@@ -738,7 +738,7 @@
         <v>1227.24</v>
       </c>
       <c r="E8" s="2">
-        <v>1750.96</v>
+        <v>1533.835</v>
       </c>
       <c r="F8">
         <v>1635</v>
@@ -748,7 +748,7 @@
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
-        <v>-523.72</v>
+        <v>-306.59500000000003</v>
       </c>
       <c r="J8" s="5"/>
     </row>
@@ -763,7 +763,7 @@
         <v>1914.65</v>
       </c>
       <c r="E9" s="2">
-        <v>1517.22</v>
+        <v>1369.69</v>
       </c>
       <c r="F9">
         <v>1110</v>
@@ -773,12 +773,12 @@
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
-        <v>397.43000000000006</v>
+        <v>544.96</v>
       </c>
       <c r="J9" s="5"/>
       <c r="L9" s="5">
         <f>SUM(I9:I15)</f>
-        <v>3542.5299999999997</v>
+        <v>3364.2089999999998</v>
       </c>
     </row>
     <row r="10" spans="2:15" x14ac:dyDescent="0.3">
@@ -807,7 +807,7 @@
       <c r="J10" s="5"/>
       <c r="L10" s="5">
         <f>L9+I6</f>
-        <v>4291.3500000000004</v>
+        <v>4088.819</v>
       </c>
     </row>
     <row r="11" spans="2:15" x14ac:dyDescent="0.3">
@@ -821,7 +821,7 @@
         <v>1942.9</v>
       </c>
       <c r="E11" s="2">
-        <v>1058.895</v>
+        <v>1118.625</v>
       </c>
       <c r="F11">
         <v>4493</v>
@@ -831,12 +831,12 @@
       </c>
       <c r="I11" s="5">
         <f t="shared" si="0"/>
-        <v>884.00500000000011</v>
+        <v>824.27500000000009</v>
       </c>
       <c r="J11" s="5"/>
       <c r="L11" s="5">
         <f>L10+I7+I8</f>
-        <v>3294.2350000000006</v>
+        <v>3308.8289999999997</v>
       </c>
     </row>
     <row r="12" spans="2:15" x14ac:dyDescent="0.3">
@@ -875,7 +875,7 @@
         <v>2185.34</v>
       </c>
       <c r="E13" s="2">
-        <v>1189.71</v>
+        <v>1272.4169999999999</v>
       </c>
       <c r="F13">
         <v>1436</v>
@@ -885,7 +885,7 @@
       </c>
       <c r="I13" s="5">
         <f t="shared" si="0"/>
-        <v>995.63000000000011</v>
+        <v>912.92300000000023</v>
       </c>
       <c r="J13" s="5"/>
     </row>
@@ -900,7 +900,7 @@
         <v>2340.4</v>
       </c>
       <c r="E14" s="2">
-        <v>2108.04</v>
+        <v>2291.4540000000002</v>
       </c>
       <c r="F14">
         <v>2834</v>
@@ -910,7 +910,7 @@
       </c>
       <c r="I14" s="5">
         <f t="shared" si="0"/>
-        <v>232.36000000000013</v>
+        <v>48.945999999999913</v>
       </c>
       <c r="J14" s="5"/>
     </row>
@@ -953,7 +953,7 @@
         <v>2426.84</v>
       </c>
       <c r="E16" s="2">
-        <v>1460.1</v>
+        <v>1466.67</v>
       </c>
       <c r="F16">
         <v>2735</v>
@@ -963,7 +963,7 @@
       </c>
       <c r="I16" s="5">
         <f t="shared" si="0"/>
-        <v>966.74000000000024</v>
+        <v>960.17000000000007</v>
       </c>
       <c r="J16" s="5"/>
     </row>
@@ -1116,19 +1116,19 @@
     <row r="27" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P27">
         <f>SUM(E3:E16)</f>
-        <v>15332.005000000003</v>
+        <v>15357.270999999999</v>
       </c>
     </row>
     <row r="28" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P28">
         <f>14468.56-P27</f>
-        <v>-863.44500000000335</v>
+        <v>-888.71099999999933</v>
       </c>
     </row>
     <row r="29" spans="2:16" x14ac:dyDescent="0.3">
       <c r="P29">
         <f>P28+2135.09</f>
-        <v>1271.6449999999968</v>
+        <v>1246.3790000000008</v>
       </c>
     </row>
     <row r="34" spans="8:8" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B54CDAE3-6C67-45A5-984D-FD9FC6B3F0F2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50AD89F-3513-4496-BDE8-1FE1E06AFAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-45" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EAP_PRODUCAO" sheetId="2" r:id="rId1"/>
@@ -978,7 +978,8 @@
         <v>2545.85</v>
       </c>
       <c r="E17" s="2">
-        <v>1255.723</v>
+        <f>85.03+1854.823</f>
+        <v>1939.8530000000001</v>
       </c>
       <c r="F17">
         <v>2361</v>
@@ -988,7 +989,7 @@
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>1290.127</v>
+        <v>605.99699999999984</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B50AD89F-3513-4496-BDE8-1FE1E06AFAE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F78BF9B9-22CB-4051-8A61-B1C4AADCE1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="2352" yWindow="2664" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EAP_PRODUCAO" sheetId="2" r:id="rId1"/>
@@ -978,8 +978,7 @@
         <v>2545.85</v>
       </c>
       <c r="E17" s="2">
-        <f>85.03+1854.823</f>
-        <v>1939.8530000000001</v>
+        <v>1992.473</v>
       </c>
       <c r="F17">
         <v>2361</v>
@@ -989,7 +988,7 @@
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>605.99699999999984</v>
+        <v>553.37699999999995</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F78BF9B9-22CB-4051-8A61-B1C4AADCE1D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FDC676-4118-4A7C-8BEA-C1702E5B00C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2352" yWindow="2664" windowWidth="17280" windowHeight="8880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EAP_PRODUCAO" sheetId="2" r:id="rId1"/>
@@ -722,7 +722,7 @@
         <v>584</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I17" si="0">D7-E7</f>
+        <f t="shared" ref="I7:I18" si="0">D7-E7</f>
         <v>-473.39499999999998</v>
       </c>
       <c r="J7" s="5"/>
@@ -1001,11 +1001,18 @@
       <c r="D18" s="3">
         <v>3108.25</v>
       </c>
+      <c r="E18" s="2">
+        <v>236.54</v>
+      </c>
       <c r="F18">
         <v>2874</v>
       </c>
       <c r="G18">
         <v>0</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>2871.71</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F4FDC676-4118-4A7C-8BEA-C1702E5B00C4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7176E514-E7B4-4911-A7DA-182A6307FBBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1002,7 +1002,7 @@
         <v>3108.25</v>
       </c>
       <c r="E18" s="2">
-        <v>236.54</v>
+        <v>426.495</v>
       </c>
       <c r="F18">
         <v>2874</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
-        <v>2871.71</v>
+        <v>2681.7550000000001</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7176E514-E7B4-4911-A7DA-182A6307FBBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE410FCB-B71F-4E1E-A256-20A7D14B44C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1002,7 +1002,7 @@
         <v>3108.25</v>
       </c>
       <c r="E18" s="2">
-        <v>426.495</v>
+        <v>600.745</v>
       </c>
       <c r="F18">
         <v>2874</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
-        <v>2681.7550000000001</v>
+        <v>2507.5050000000001</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE410FCB-B71F-4E1E-A256-20A7D14B44C5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EA240C-C5B6-41AD-B363-538FFEB32C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1002,7 +1002,7 @@
         <v>3108.25</v>
       </c>
       <c r="E18" s="2">
-        <v>600.745</v>
+        <v>670.245</v>
       </c>
       <c r="F18">
         <v>2874</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
-        <v>2507.5050000000001</v>
+        <v>2438.0050000000001</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{92EA240C-C5B6-41AD-B363-538FFEB32C51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F103FEA-E0E6-4D2E-92C1-5A5B95109940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1002,7 +1002,8 @@
         <v>3108.25</v>
       </c>
       <c r="E18" s="2">
-        <v>670.245</v>
+        <f>1014.545+57.846</f>
+        <v>1072.3909999999998</v>
       </c>
       <c r="F18">
         <v>2874</v>
@@ -1012,7 +1013,7 @@
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
-        <v>2438.0050000000001</v>
+        <v>2035.8590000000002</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2F103FEA-E0E6-4D2E-92C1-5A5B95109940}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9E68C5-882F-4B9F-A87D-D58417762720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EAP_PRODUCAO" sheetId="2" r:id="rId1"/>
@@ -1002,8 +1002,7 @@
         <v>3108.25</v>
       </c>
       <c r="E18" s="2">
-        <f>1014.545+57.846</f>
-        <v>1072.3909999999998</v>
+        <v>1307.3900000000001</v>
       </c>
       <c r="F18">
         <v>2874</v>
@@ -1013,7 +1012,7 @@
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
-        <v>2035.8590000000002</v>
+        <v>1800.86</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B9E68C5-882F-4B9F-A87D-D58417762720}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B6C26A-498B-4012-B2D6-84B94A6BD1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EAP_PRODUCAO" sheetId="2" r:id="rId1"/>
@@ -1002,7 +1002,7 @@
         <v>3108.25</v>
       </c>
       <c r="E18" s="2">
-        <v>1307.3900000000001</v>
+        <v>1384.8910000000001</v>
       </c>
       <c r="F18">
         <v>2874</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
-        <v>1800.86</v>
+        <v>1723.3589999999999</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1B6C26A-498B-4012-B2D6-84B94A6BD1B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8900B8A9-2E78-44B9-AE67-C4ABEB1DF9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1002,7 +1002,7 @@
         <v>3108.25</v>
       </c>
       <c r="E18" s="2">
-        <v>1384.8910000000001</v>
+        <v>1495.3910000000001</v>
       </c>
       <c r="F18">
         <v>2874</v>
@@ -1012,7 +1012,7 @@
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
-        <v>1723.3589999999999</v>
+        <v>1612.8589999999999</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8900B8A9-2E78-44B9-AE67-C4ABEB1DF9BE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08B53EA-FE7F-4BCD-AF06-F035C77144C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="21">
   <si>
     <t>Ano</t>
   </si>
@@ -93,6 +93,9 @@
   </si>
   <si>
     <t>mar de coral esta com o valor de as built</t>
+  </si>
+  <si>
+    <t>TL-0 Recebidas</t>
   </si>
 </sst>
 </file>
@@ -590,6 +593,7 @@
     <col min="5" max="5" width="13.21875" customWidth="1"/>
     <col min="6" max="6" width="15.77734375" customWidth="1"/>
     <col min="7" max="7" width="19.5546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.109375" customWidth="1"/>
     <col min="9" max="10" width="9.33203125" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
@@ -613,6 +617,9 @@
       <c r="G2" s="1" t="s">
         <v>17</v>
       </c>
+      <c r="H2" s="1" t="s">
+        <v>20</v>
+      </c>
     </row>
     <row r="3" spans="2:15" x14ac:dyDescent="0.3">
       <c r="B3" s="2">
@@ -984,7 +991,10 @@
         <v>2361</v>
       </c>
       <c r="G17">
-        <v>0</v>
+        <v>87</v>
+      </c>
+      <c r="H17">
+        <v>189</v>
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C08B53EA-FE7F-4BCD-AF06-F035C77144C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B42F72-606E-4A9C-9BDE-CE139133510A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1012,7 +1012,7 @@
         <v>3108.25</v>
       </c>
       <c r="E18" s="2">
-        <v>1495.3910000000001</v>
+        <v>1524.3910000000001</v>
       </c>
       <c r="F18">
         <v>2874</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
-        <v>1612.8589999999999</v>
+        <v>1583.8589999999999</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{05B42F72-606E-4A9C-9BDE-CE139133510A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95249EB5-ECF0-408A-BCF3-3BA976DCDBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1012,7 +1012,7 @@
         <v>3108.25</v>
       </c>
       <c r="E18" s="2">
-        <v>1524.3910000000001</v>
+        <v>1883.491</v>
       </c>
       <c r="F18">
         <v>2874</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
-        <v>1583.8589999999999</v>
+        <v>1224.759</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{95249EB5-ECF0-408A-BCF3-3BA976DCDBCA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582B2045-271D-44A5-AD11-CD06CF7902B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EAP_PRODUCAO" sheetId="2" r:id="rId1"/>
@@ -729,7 +729,7 @@
         <v>584</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" ref="I7:I18" si="0">D7-E7</f>
+        <f t="shared" ref="I7:I19" si="0">D7-E7</f>
         <v>-473.39499999999998</v>
       </c>
       <c r="J7" s="5"/>
@@ -1035,11 +1035,18 @@
       <c r="D19" s="3">
         <v>3269.49</v>
       </c>
+      <c r="E19" s="2">
+        <v>405.2</v>
+      </c>
       <c r="F19">
         <v>4487</v>
       </c>
       <c r="G19">
         <v>0</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>2864.29</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{582B2045-271D-44A5-AD11-CD06CF7902B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46264610-EC5E-4720-890F-4D3F5AF98960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -985,7 +985,7 @@
         <v>2545.85</v>
       </c>
       <c r="E17" s="2">
-        <v>1992.473</v>
+        <v>2071.5729999999999</v>
       </c>
       <c r="F17">
         <v>2361</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>553.37699999999995</v>
+        <v>474.27700000000004</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
@@ -1012,7 +1012,7 @@
         <v>3108.25</v>
       </c>
       <c r="E18" s="2">
-        <v>1883.491</v>
+        <v>1814.491</v>
       </c>
       <c r="F18">
         <v>2874</v>
@@ -1022,7 +1022,7 @@
       </c>
       <c r="I18" s="5">
         <f t="shared" si="0"/>
-        <v>1224.759</v>
+        <v>1293.759</v>
       </c>
     </row>
     <row r="19" spans="2:16" x14ac:dyDescent="0.3">
@@ -1036,7 +1036,7 @@
         <v>3269.49</v>
       </c>
       <c r="E19" s="2">
-        <v>405.2</v>
+        <v>439.7</v>
       </c>
       <c r="F19">
         <v>4487</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
-        <v>2864.29</v>
+        <v>2829.79</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{46264610-EC5E-4720-890F-4D3F5AF98960}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4326D0D5-AA73-4B57-8975-2617567A25D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1036,7 +1036,7 @@
         <v>3269.49</v>
       </c>
       <c r="E19" s="2">
-        <v>439.7</v>
+        <v>753.5</v>
       </c>
       <c r="F19">
         <v>4487</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
-        <v>2829.79</v>
+        <v>2515.9899999999998</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4326D0D5-AA73-4B57-8975-2617567A25D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DB9CAA-926C-48AC-8FDE-425FB286B20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="EAP_PRODUCAO" sheetId="2" r:id="rId1"/>
@@ -1036,7 +1036,7 @@
         <v>3269.49</v>
       </c>
       <c r="E19" s="2">
-        <v>753.5</v>
+        <v>800.5</v>
       </c>
       <c r="F19">
         <v>4487</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
-        <v>2515.9899999999998</v>
+        <v>2468.9899999999998</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3DB9CAA-926C-48AC-8FDE-425FB286B20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542AC259-1B89-4631-A881-DE317B2EA47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1036,7 +1036,7 @@
         <v>3269.49</v>
       </c>
       <c r="E19" s="2">
-        <v>800.5</v>
+        <v>1008.2</v>
       </c>
       <c r="F19">
         <v>4487</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
-        <v>2468.9899999999998</v>
+        <v>2261.29</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">

--- a/docs/EAP_PRODUCAO.xlsx
+++ b/docs/EAP_PRODUCAO.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\micro\Desktop\moderno\dashboard-obras\github\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{542AC259-1B89-4631-A881-DE317B2EA47E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C9CE2B2-3D0C-43D1-BA20-EB24DA02E392}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -985,7 +985,7 @@
         <v>2545.85</v>
       </c>
       <c r="E17" s="2">
-        <v>2071.5729999999999</v>
+        <v>1994.873</v>
       </c>
       <c r="F17">
         <v>2361</v>
@@ -998,7 +998,7 @@
       </c>
       <c r="I17" s="5">
         <f t="shared" si="0"/>
-        <v>474.27700000000004</v>
+        <v>550.97699999999986</v>
       </c>
     </row>
     <row r="18" spans="2:16" x14ac:dyDescent="0.3">
@@ -1036,7 +1036,7 @@
         <v>3269.49</v>
       </c>
       <c r="E19" s="2">
-        <v>1008.2</v>
+        <v>1047.04</v>
       </c>
       <c r="F19">
         <v>4487</v>
@@ -1046,7 +1046,7 @@
       </c>
       <c r="I19" s="5">
         <f t="shared" si="0"/>
-        <v>2261.29</v>
+        <v>2222.4499999999998</v>
       </c>
     </row>
     <row r="20" spans="2:16" x14ac:dyDescent="0.3">
